--- a/design/KUROTSUKI_Personaje.xlsx
+++ b/design/KUROTSUKI_Personaje.xlsx
@@ -2,28 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Citeste-ma" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Stats" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Personaje" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Abilități" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Upgrade-uri_stil" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Sumar" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Note-implementare" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Decizii-finale" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stats" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Personaje" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Abilități" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Upgrade-uri_stil" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sumar" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Note-implementare" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,14 +32,41 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <i val="1"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -48,7 +75,51 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1F2A44"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F2A44"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B6B6"/>
       </patternFill>
     </fill>
     <fill>
@@ -58,14 +129,369 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
+        <fgColor rgb="00F8D5E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6E6C1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B9A6D6"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="27">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -88,7 +514,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -105,79 +531,220 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -473,74 +1040,74 @@
   <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="140" customWidth="1" min="1" max="1"/>
+    <col width="161.42578125" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>KUROTSUKI: ENDLESS NIGHT — personaje</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Foi: Stats (toate stat-urile, per personaj), Personaje (rol, armă, pasivă), Abilități (LMB, RMB, Shift, Q, E per personaj), Upgrade-uri_stil (idei pentru stilurile noi), Sumar (comparație), Note-implementare.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Rândurile gri sunt ce EXISTĂ deja în joc (Kazuma). Restul sunt propuneri noi de la mine, ca punct de pornire.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Ce completezi tu: coloanele GALBENE. În Decizie alegi din listă: DA, NU, MODIFIC sau DE DISCUTAT; în Comentarii scrii ce vrei schimbat. În foaia Stats poți scrie direct valorile tale în coloanele galbene.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>REGULI DEJA DECISE: toate personajele sunt deblocate de la început; se aleg într-un ecran Character Select după ce alegi modul de joc (Quick / Standard).</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Fiecare personaj are: Stats diferite (~±20%), O SINGURĂ pasivă, armă proprie și 5 sloturi diferite: LMB (atac de bază), RMB, Shift, Q, E.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>TOATE personajele folosesc același sistem Kata (Opening → Flow → Finisher + Master). RMB rămâne Finisher-ul Kata-ului pentru toți (doar forma loviturii diferă după armă). Upgrade-uri care favorizează stilurile celorlalte personaje vin după ce stabilim personajele.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>E (Ultimate) se încarcă DOAR din kill-uri, la toți. Fără schimburi de viață pentru aur.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Stat-urile din foaia Stats sunt cele reale din joc (StatsComponent). „Bază actuală" = valoarea de azi pentru Kazuma. Tip: plat = număr adăugat, multiplicator = 1,0 înseamnă neschimbat (1,2 = +20%).</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="10" ht="30" customHeight="1" thickBot="1">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Numele sunt în engleză (cum apar în joc), descrierile în română. Valorile sunt puncte de plecare; le ajustăm la testare.</t>
         </is>
@@ -552,6 +1119,1063 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="68" t="inlineStr">
+        <is>
+          <t>DECIZII FINALE (rezumat din completările tale + răspunsurile din chat). Coloana galbenă = de confirmat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="69" t="inlineStr">
+        <is>
+          <t>Personaj</t>
+        </is>
+      </c>
+      <c r="B3" s="69" t="inlineStr">
+        <is>
+          <t>Categorie</t>
+        </is>
+      </c>
+      <c r="C3" s="69" t="inlineStr">
+        <is>
+          <t>Ales</t>
+        </is>
+      </c>
+      <c r="D3" s="69" t="inlineStr">
+        <is>
+          <t>Detalii / valori</t>
+        </is>
+      </c>
+      <c r="E3" s="69" t="inlineStr">
+        <is>
+          <t>De confirmat</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="70" t="inlineStr">
+        <is>
+          <t>Kazuma</t>
+        </is>
+      </c>
+      <c r="B4" s="70" t="inlineStr">
+        <is>
+          <t>Culoare placeholder</t>
+        </is>
+      </c>
+      <c r="C4" s="70" t="inlineStr">
+        <is>
+          <t>Roșu</t>
+        </is>
+      </c>
+      <c r="D4" s="70" t="inlineStr">
+        <is>
+          <t>Până apar modelele din Blender, personajul are corp și armă simple în această culoare.</t>
+        </is>
+      </c>
+      <c r="E4" s="70" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="71" t="inlineStr">
+        <is>
+          <t>Kazuma</t>
+        </is>
+      </c>
+      <c r="B5" s="71" t="inlineStr">
+        <is>
+          <t>Armă</t>
+        </is>
+      </c>
+      <c r="C5" s="71" t="inlineStr">
+        <is>
+          <t>Katana</t>
+        </is>
+      </c>
+      <c r="D5" s="71" t="inlineStr">
+        <is>
+          <t>Arma actuală din joc.</t>
+        </is>
+      </c>
+      <c r="E5" s="71" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="71" t="inlineStr">
+        <is>
+          <t>Kazuma</t>
+        </is>
+      </c>
+      <c r="B6" s="71" t="inlineStr">
+        <is>
+          <t>Pasivă</t>
+        </is>
+      </c>
+      <c r="C6" s="71" t="inlineStr">
+        <is>
+          <t>A – Keen Eye</t>
+        </is>
+      </c>
+      <c r="D6" s="71" t="inlineStr">
+        <is>
+          <t>+8% șansă critică permanent.</t>
+        </is>
+      </c>
+      <c r="E6" s="72" t="inlineStr">
+        <is>
+          <t>B și C = NU, A nu era bifat: o iau ca DA?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="71" t="inlineStr">
+        <is>
+          <t>Kazuma</t>
+        </is>
+      </c>
+      <c r="B7" s="71" t="inlineStr">
+        <is>
+          <t>LMB</t>
+        </is>
+      </c>
+      <c r="C7" s="71" t="inlineStr">
+        <is>
+          <t>Katana Slash</t>
+        </is>
+      </c>
+      <c r="D7" s="71" t="inlineStr">
+        <is>
+          <t>Damage 11 (damage de bază).</t>
+        </is>
+      </c>
+      <c r="E7" s="71" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="71" t="inlineStr">
+        <is>
+          <t>Kazuma</t>
+        </is>
+      </c>
+      <c r="B8" s="71" t="inlineStr">
+        <is>
+          <t>RMB</t>
+        </is>
+      </c>
+      <c r="C8" s="71" t="inlineStr">
+        <is>
+          <t>Heavy (Finisher Kata)</t>
+        </is>
+      </c>
+      <c r="D8" s="71" t="inlineStr">
+        <is>
+          <t>Damage 15 = damage de bază + 4 PLAT. Heavy-ul de azi (1,8×) se schimbă.</t>
+        </is>
+      </c>
+      <c r="E8" s="71" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="71" t="inlineStr">
+        <is>
+          <t>Kazuma</t>
+        </is>
+      </c>
+      <c r="B9" s="71" t="inlineStr">
+        <is>
+          <t>Shift</t>
+        </is>
+      </c>
+      <c r="C9" s="71" t="inlineStr">
+        <is>
+          <t>Iaijutsu</t>
+        </is>
+      </c>
+      <c r="D9" s="71" t="inlineStr">
+        <is>
+          <t>Damage 11 = 1,0× damage de bază (azi 2,2×).</t>
+        </is>
+      </c>
+      <c r="E9" s="71" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="71" t="inlineStr">
+        <is>
+          <t>Kazuma</t>
+        </is>
+      </c>
+      <c r="B10" s="71" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C10" s="71" t="inlineStr">
+        <is>
+          <t>Kaeshi</t>
+        </is>
+      </c>
+      <c r="D10" s="71" t="inlineStr">
+        <is>
+          <t>NESCHIMBAT, păstrat cum era (nota ta cu 40% din atacul parat NU se aplică, după ce ai ales să rămână ca până acum).</t>
+        </is>
+      </c>
+      <c r="E10" s="71" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="71" t="inlineStr">
+        <is>
+          <t>Kazuma</t>
+        </is>
+      </c>
+      <c r="B11" s="71" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C11" s="71" t="inlineStr">
+        <is>
+          <t>Moonlit Storm</t>
+        </is>
+      </c>
+      <c r="D11" s="71" t="inlineStr">
+        <is>
+          <t>Neschimbat; se încarcă doar din kill-uri.</t>
+        </is>
+      </c>
+      <c r="E11" s="71" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="71" t="inlineStr">
+        <is>
+          <t>Kazuma</t>
+        </is>
+      </c>
+      <c r="B12" s="71" t="inlineStr">
+        <is>
+          <t>Stat-uri</t>
+        </is>
+      </c>
+      <c r="C12" s="71" t="inlineStr">
+        <is>
+          <t>110 HP · 11 dmg · atac 1,0 · viteză 6,0</t>
+        </is>
+      </c>
+      <c r="D12" s="71" t="inlineStr">
+        <is>
+          <t>Celelalte stat-uri la valoarea de bază (azi Kazuma are 100 HP și 10 dmg).</t>
+        </is>
+      </c>
+      <c r="E12" s="71" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="73" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B13" s="73" t="inlineStr">
+        <is>
+          <t>Culoare placeholder</t>
+        </is>
+      </c>
+      <c r="C13" s="73" t="inlineStr">
+        <is>
+          <t>Mov deschis / Sakura</t>
+        </is>
+      </c>
+      <c r="D13" s="73" t="inlineStr"/>
+      <c r="E13" s="73" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="71" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B14" s="71" t="inlineStr">
+        <is>
+          <t>Armă</t>
+        </is>
+      </c>
+      <c r="C14" s="71" t="inlineStr">
+        <is>
+          <t>Tessen (evantaie de luptă)</t>
+        </is>
+      </c>
+      <c r="D14" s="71" t="inlineStr"/>
+      <c r="E14" s="71" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="71" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B15" s="71" t="inlineStr">
+        <is>
+          <t>Pasivă</t>
+        </is>
+      </c>
+      <c r="C15" s="71" t="inlineStr">
+        <is>
+          <t>B – Butterfly Twist</t>
+        </is>
+      </c>
+      <c r="D15" s="71" t="inlineStr">
+        <is>
+          <t>La ORICE dash (Space și Phantom Step), cu cooldown intern de 1 s, aruncă 3 shuriken (5 damage fiecare) în evantai în direcția OPUSĂ dash-ului (dash în spate → shuriken în față). Contează ca „skill”: dau Flow în Kata, încarcă E la kill, pot da critic.</t>
+        </is>
+      </c>
+      <c r="E15" s="72" t="inlineStr">
+        <is>
+          <t>Damage-ul shuriken-ului: fix 5 sau scalat cu damage-ul ei?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="71" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B16" s="71" t="inlineStr">
+        <is>
+          <t>LMB</t>
+        </is>
+      </c>
+      <c r="C16" s="71" t="inlineStr">
+        <is>
+          <t>A – Twin Cuts</t>
+        </is>
+      </c>
+      <c r="D16" s="71" t="inlineStr">
+        <is>
+          <t>Tăieturi rapide la fiecare apăsare, rază mică (cu tessen: două lovituri rapide de evantai).</t>
+        </is>
+      </c>
+      <c r="E16" s="72" t="inlineStr">
+        <is>
+          <t>OK cu tessen?</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="71" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B17" s="71" t="inlineStr">
+        <is>
+          <t>RMB</t>
+        </is>
+      </c>
+      <c r="C17" s="71" t="inlineStr">
+        <is>
+          <t>C – Leaping Cut (Finisher Kata)</t>
+        </is>
+      </c>
+      <c r="D17" s="71" t="inlineStr">
+        <is>
+          <t>Sare peste inamic și taie în spate. Damage = damage de bază + 4.</t>
+        </is>
+      </c>
+      <c r="E17" s="71" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="71" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B18" s="71" t="inlineStr">
+        <is>
+          <t>Shift</t>
+        </is>
+      </c>
+      <c r="C18" s="71" t="inlineStr">
+        <is>
+          <t>A – Phantom Step</t>
+        </is>
+      </c>
+      <c r="D18" s="71" t="inlineStr">
+        <is>
+          <t>Butterfly Twist scurt (4 m) care lasă o clonă ce taie în urmă.</t>
+        </is>
+      </c>
+      <c r="E18" s="71" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="71" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B19" s="71" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C19" s="71" t="inlineStr">
+        <is>
+          <t>C – Mirror Dream</t>
+        </is>
+      </c>
+      <c r="D19" s="71" t="inlineStr">
+        <is>
+          <t>O iluzie îi atrage atacurile 2 s, apoi explodează. Explozia afectează DOAR inamicii.</t>
+        </is>
+      </c>
+      <c r="E19" s="71" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="71" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B20" s="71" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C20" s="71" t="inlineStr">
+        <is>
+          <t>B – Dream Clones</t>
+        </is>
+      </c>
+      <c r="D20" s="71" t="inlineStr">
+        <is>
+          <t>3 clone atacă 4 secunde.</t>
+        </is>
+      </c>
+      <c r="E20" s="71" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="71" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B21" s="71" t="inlineStr">
+        <is>
+          <t>Stat-uri</t>
+        </is>
+      </c>
+      <c r="C21" s="71" t="inlineStr">
+        <is>
+          <t>85 HP · 9 dmg · atac 1,2 · viteză 7,0</t>
+        </is>
+      </c>
+      <c r="D21" s="71" t="inlineStr">
+        <is>
+          <t>Critic 5%, dash recharge ×1,2, distanță dash ×1,1.</t>
+        </is>
+      </c>
+      <c r="E21" s="71" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="74" t="inlineStr">
+        <is>
+          <t>Takeda</t>
+        </is>
+      </c>
+      <c r="B22" s="74" t="inlineStr">
+        <is>
+          <t>Culoare placeholder</t>
+        </is>
+      </c>
+      <c r="C22" s="74" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="D22" s="74" t="inlineStr"/>
+      <c r="E22" s="74" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="71" t="inlineStr">
+        <is>
+          <t>Takeda</t>
+        </is>
+      </c>
+      <c r="B23" s="71" t="inlineStr">
+        <is>
+          <t>Armă</t>
+        </is>
+      </c>
+      <c r="C23" s="71" t="inlineStr">
+        <is>
+          <t>Kanabō (ciomag de fier)</t>
+        </is>
+      </c>
+      <c r="D23" s="71" t="inlineStr">
+        <is>
+          <t>Lovituri de zdrobire, knockback și unde de șoc.</t>
+        </is>
+      </c>
+      <c r="E23" s="71" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="71" t="inlineStr">
+        <is>
+          <t>Takeda</t>
+        </is>
+      </c>
+      <c r="B24" s="71" t="inlineStr">
+        <is>
+          <t>Pasivă</t>
+        </is>
+      </c>
+      <c r="C24" s="71" t="inlineStr">
+        <is>
+          <t>B – Heavy Hand</t>
+        </is>
+      </c>
+      <c r="D24" s="71" t="inlineStr">
+        <is>
+          <t>RMB: +15% damage, +10% rază și KNOCKBACK pe inamici.</t>
+        </is>
+      </c>
+      <c r="E24" s="71" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="71" t="inlineStr">
+        <is>
+          <t>Takeda</t>
+        </is>
+      </c>
+      <c r="B25" s="71" t="inlineStr">
+        <is>
+          <t>LMB</t>
+        </is>
+      </c>
+      <c r="C25" s="71" t="inlineStr">
+        <is>
+          <t>B – Wide Sweep</t>
+        </is>
+      </c>
+      <c r="D25" s="71" t="inlineStr">
+        <is>
+          <t>Mătură lentă într-un arc de 200°.</t>
+        </is>
+      </c>
+      <c r="E25" s="71" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="71" t="inlineStr">
+        <is>
+          <t>Takeda</t>
+        </is>
+      </c>
+      <c r="B26" s="71" t="inlineStr">
+        <is>
+          <t>RMB</t>
+        </is>
+      </c>
+      <c r="C26" s="71" t="inlineStr">
+        <is>
+          <t>A – Earth Crush (Finisher Kata)</t>
+        </is>
+      </c>
+      <c r="D26" s="71" t="inlineStr">
+        <is>
+          <t>Lovitură verticală cu undă de șoc în fața lui. Damage = damage de bază + 4.</t>
+        </is>
+      </c>
+      <c r="E26" s="71" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="71" t="inlineStr">
+        <is>
+          <t>Takeda</t>
+        </is>
+      </c>
+      <c r="B27" s="71" t="inlineStr">
+        <is>
+          <t>Shift</t>
+        </is>
+      </c>
+      <c r="C27" s="71" t="inlineStr">
+        <is>
+          <t>A – Shield Charge</t>
+        </is>
+      </c>
+      <c r="D27" s="71" t="inlineStr">
+        <is>
+          <t>Înaintează 4 m cu umărul și împinge inamicii (invulnerabil la început). Inamicii împinși într-un obstacol/perete sunt ametiți. COOLDOWN 8 s față de 6 s la ceilalți (Space dash rămâne ca în Stats).</t>
+        </is>
+      </c>
+      <c r="E27" s="71" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="71" t="inlineStr">
+        <is>
+          <t>Takeda</t>
+        </is>
+      </c>
+      <c r="B28" s="71" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C28" s="71" t="inlineStr">
+        <is>
+          <t>B – Stone Stance</t>
+        </is>
+      </c>
+      <c r="D28" s="71" t="inlineStr">
+        <is>
+          <t>5 s de armură: −60% damage primit. Mișcare −30% în timpul ei, cooldown 14 s.</t>
+        </is>
+      </c>
+      <c r="E28" s="71" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="71" t="inlineStr">
+        <is>
+          <t>Takeda</t>
+        </is>
+      </c>
+      <c r="B29" s="71" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C29" s="71" t="inlineStr">
+        <is>
+          <t>A – The Mountain</t>
+        </is>
+      </c>
+      <c r="D29" s="71" t="inlineStr">
+        <is>
+          <t>5 s de unde de șoc repetate în jurul lui Takeda (se mișcă cu el, el rămâne în centru): rază ~4 m, o undă la ~0,6 s, ~70% din damage-ul de bază + knockback.</t>
+        </is>
+      </c>
+      <c r="E29" s="71" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="71" t="inlineStr">
+        <is>
+          <t>Takeda</t>
+        </is>
+      </c>
+      <c r="B30" s="71" t="inlineStr">
+        <is>
+          <t>Stat-uri</t>
+        </is>
+      </c>
+      <c r="C30" s="71" t="inlineStr">
+        <is>
+          <t>130 HP · 12 dmg · atac 0,85 · viteză 5,2</t>
+        </is>
+      </c>
+      <c r="D30" s="71" t="inlineStr">
+        <is>
+          <t>Damage primit ×0,9, heavy ×1,2, rază heavy ×1,15, dash recharge ×0,9, distanță dash ×0,9.</t>
+        </is>
+      </c>
+      <c r="E30" s="71" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="75" t="inlineStr">
+        <is>
+          <t>Kurotsuki</t>
+        </is>
+      </c>
+      <c r="B31" s="75" t="inlineStr">
+        <is>
+          <t>Culoare placeholder</t>
+        </is>
+      </c>
+      <c r="C31" s="75" t="inlineStr">
+        <is>
+          <t>Mov închis / negru</t>
+        </is>
+      </c>
+      <c r="D31" s="75" t="inlineStr"/>
+      <c r="E31" s="75" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="71" t="inlineStr">
+        <is>
+          <t>Kurotsuki</t>
+        </is>
+      </c>
+      <c r="B32" s="71" t="inlineStr">
+        <is>
+          <t>Armă</t>
+        </is>
+      </c>
+      <c r="C32" s="71" t="inlineStr">
+        <is>
+          <t>Gheare de oțel (tekko-kagi)</t>
+        </is>
+      </c>
+      <c r="D32" s="71" t="inlineStr">
+        <is>
+          <t>Lovituri rapide la distanță mică.</t>
+        </is>
+      </c>
+      <c r="E32" s="71" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="71" t="inlineStr">
+        <is>
+          <t>Kurotsuki</t>
+        </is>
+      </c>
+      <c r="B33" s="71" t="inlineStr">
+        <is>
+          <t>Pasivă</t>
+        </is>
+      </c>
+      <c r="C33" s="71" t="inlineStr">
+        <is>
+          <t>C – Born Cursed</t>
+        </is>
+      </c>
+      <c r="D33" s="71" t="inlineStr">
+        <is>
+          <t>Începe fiecare run cu 15% Corruption, iar upgrade-urile Cursed sunt deblocate din start (stat nou starting_corruption).</t>
+        </is>
+      </c>
+      <c r="E33" s="71" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="71" t="inlineStr">
+        <is>
+          <t>Kurotsuki</t>
+        </is>
+      </c>
+      <c r="B34" s="71" t="inlineStr">
+        <is>
+          <t>LMB</t>
+        </is>
+      </c>
+      <c r="C34" s="71" t="inlineStr">
+        <is>
+          <t>A – Cursed Edge</t>
+        </is>
+      </c>
+      <c r="D34" s="71" t="inlineStr">
+        <is>
+          <t>Lovituri cu o mică șansă de bleed.</t>
+        </is>
+      </c>
+      <c r="E34" s="71" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="71" t="inlineStr">
+        <is>
+          <t>Kurotsuki</t>
+        </is>
+      </c>
+      <c r="B35" s="71" t="inlineStr">
+        <is>
+          <t>RMB</t>
+        </is>
+      </c>
+      <c r="C35" s="71" t="inlineStr">
+        <is>
+          <t>A – Blood Cut (Finisher Kata)</t>
+        </is>
+      </c>
+      <c r="D35" s="71" t="inlineStr">
+        <is>
+          <t>Aplică bleed (3 stack-uri) pe toate țintele. Damage = damage de bază + 4.</t>
+        </is>
+      </c>
+      <c r="E35" s="71" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="71" t="inlineStr">
+        <is>
+          <t>Kurotsuki</t>
+        </is>
+      </c>
+      <c r="B36" s="71" t="inlineStr">
+        <is>
+          <t>Shift</t>
+        </is>
+      </c>
+      <c r="C36" s="71" t="inlineStr">
+        <is>
+          <t>A – Shadow Pass</t>
+        </is>
+      </c>
+      <c r="D36" s="71" t="inlineStr">
+        <is>
+          <t>Dash prin inamici care lasă o zonă de bleed.</t>
+        </is>
+      </c>
+      <c r="E36" s="71" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="71" t="inlineStr">
+        <is>
+          <t>Kurotsuki</t>
+        </is>
+      </c>
+      <c r="B37" s="71" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="C37" s="71" t="inlineStr">
+        <is>
+          <t>A – Absorb</t>
+        </is>
+      </c>
+      <c r="D37" s="71" t="inlineStr">
+        <is>
+          <t>Consumă 20 Corruption pentru a vindeca 15% HP (nu se poate cât ești Possessed).</t>
+        </is>
+      </c>
+      <c r="E37" s="71" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="71" t="inlineStr">
+        <is>
+          <t>Kurotsuki</t>
+        </is>
+      </c>
+      <c r="B38" s="71" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C38" s="71" t="inlineStr">
+        <is>
+          <t>A – Awakening</t>
+        </is>
+      </c>
+      <c r="D38" s="71" t="inlineStr">
+        <is>
+          <t>Intri imediat în Possessed (cere Corruption ≥ 50%). Efectele sunt ×1,25 față de ceilalți și durează 18 s: +31% viteză, +37% viteză atac, +75% damage, −56% damage primit, lifesteal 12,5%.</t>
+        </is>
+      </c>
+      <c r="E38" s="71" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="71" t="inlineStr">
+        <is>
+          <t>Kurotsuki</t>
+        </is>
+      </c>
+      <c r="B39" s="71" t="inlineStr">
+        <is>
+          <t>Stat-uri</t>
+        </is>
+      </c>
+      <c r="C39" s="71" t="inlineStr">
+        <is>
+          <t>95 HP · 10,5 dmg · atac 1,1 · viteză 6,2</t>
+        </is>
+      </c>
+      <c r="D39" s="71" t="inlineStr">
+        <is>
+          <t>Bleed ×1,2.</t>
+        </is>
+      </c>
+      <c r="E39" s="71" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="68" t="inlineStr">
+        <is>
+          <t>REGULI GLOBALE NOI (se aplică din C1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="69" t="inlineStr"/>
+      <c r="B43" s="69" t="inlineStr">
+        <is>
+          <t>Zonă</t>
+        </is>
+      </c>
+      <c r="C43" s="69" t="inlineStr">
+        <is>
+          <t>Regulă</t>
+        </is>
+      </c>
+      <c r="D43" s="69" t="inlineStr">
+        <is>
+          <t>Detalii</t>
+        </is>
+      </c>
+      <c r="E43" s="69" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="71" t="inlineStr"/>
+      <c r="B44" s="71" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C44" s="71" t="inlineStr">
+        <is>
+          <t>RMB = damage de bază + 4 plat</t>
+        </is>
+      </c>
+      <c r="D44" s="71" t="inlineStr">
+        <is>
+          <t>Apoi se aplică heavy_damage (ex. Takeda ×1,2, +15% din pasivă) și multiplicatorii Kata ai Finisher-ului. Până acum Heavy era 1,8×; Iaijutsu 2,2× → acum 1,0×. Posibil să reechilibrăm inamicii/upgrade-urile la testare.</t>
+        </is>
+      </c>
+      <c r="E44" s="71" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="71" t="inlineStr"/>
+      <c r="B45" s="71" t="inlineStr">
+        <is>
+          <t>Lifesteal</t>
+        </is>
+      </c>
+      <c r="C45" s="71" t="inlineStr">
+        <is>
+          <t>Toate vindecările „la kill” devin lifesteal (HP din damage dat)</t>
+        </is>
+      </c>
+      <c r="D45" s="71" t="inlineStr">
+        <is>
+          <t>Stat nou lifesteal (înlocuiește life_on_kill). Moderat: Crimson Meal 6%, Bloodthirst 2%, Blood Harvest 10% din damage-ul Finisher-ului, Sakura Charm 15% din Finisher, Soul Syphon 50% din tick-ul de bleed. Possessed rămâne 10%.</t>
+        </is>
+      </c>
+      <c r="E45" s="71" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="71" t="inlineStr"/>
+      <c r="B46" s="71" t="inlineStr">
+        <is>
+          <t>Stat-uri noi</t>
+        </is>
+      </c>
+      <c r="C46" s="71" t="inlineStr">
+        <is>
+          <t>attack_range, starting_corruption, lifesteal</t>
+        </is>
+      </c>
+      <c r="D46" s="71" t="inlineStr">
+        <is>
+          <t>attack_range pentru „Weapon Master” (+15% rază LMB, la toți); starting_corruption pentru Kurotsuki; lifesteal pentru regula de mai sus.</t>
+        </is>
+      </c>
+      <c r="E46" s="71" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="71" t="inlineStr"/>
+      <c r="B47" s="71" t="inlineStr">
+        <is>
+          <t>Kata</t>
+        </is>
+      </c>
+      <c r="C47" s="71" t="inlineStr">
+        <is>
+          <t>Comun pentru toți</t>
+        </is>
+      </c>
+      <c r="D47" s="71" t="inlineStr">
+        <is>
+          <t>Tehnicile legate de skill-uri se leagă de SLOT (Shift / Q), nu de nume. Opening-ul „Crescent Entry” = tăietura de pe Shift; „Shadow Vault” = efectul de pe Q (la Kaeshi contra reușită; la Yume Mirror Dream; la Takeda Stone Stance; la Kurotsuki Absorb).</t>
+        </is>
+      </c>
+      <c r="E47" s="71" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="71" t="inlineStr"/>
+      <c r="B48" s="71" t="inlineStr">
+        <is>
+          <t>Selecție</t>
+        </is>
+      </c>
+      <c r="C48" s="71" t="inlineStr">
+        <is>
+          <t>Character Select după alegerea modului</t>
+        </is>
+      </c>
+      <c r="D48" s="71" t="inlineStr">
+        <is>
+          <t>Toate personajele deblocate de la început.</t>
+        </is>
+      </c>
+      <c r="E48" s="71" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="71" t="inlineStr"/>
+      <c r="B49" s="71" t="inlineStr">
+        <is>
+          <t>Upgrade-uri de stil</t>
+        </is>
+      </c>
+      <c r="C49" s="71" t="inlineStr">
+        <is>
+          <t>Personajul țintă are șansă ~3× mai mare</t>
+        </is>
+      </c>
+      <c r="D49" s="71" t="inlineStr">
+        <is>
+          <t>Nu sunt exclusive: oricine le poate găsi. „Weapon Master” apare la toți. Toate DA, în afară de „Iron Stance” (NU).</t>
+        </is>
+      </c>
+      <c r="E49" s="71" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="71" t="inlineStr"/>
+      <c r="B50" s="71" t="inlineStr">
+        <is>
+          <t>Dash</t>
+        </is>
+      </c>
+      <c r="C50" s="71" t="inlineStr">
+        <is>
+          <t>dodge_charges</t>
+        </is>
+      </c>
+      <c r="D50" s="71" t="inlineStr">
+        <is>
+          <t>Rămâne 1 la toate personajele; upgrade-urile existente îl pot crește.</t>
+        </is>
+      </c>
+      <c r="E50" s="71" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="71" t="inlineStr"/>
+      <c r="B51" s="71" t="inlineStr">
+        <is>
+          <t>Ordine implementare</t>
+        </is>
+      </c>
+      <c r="C51" s="71" t="inlineStr">
+        <is>
+          <t>C1 → Yume → Takeda → Kurotsuki</t>
+        </is>
+      </c>
+      <c r="D51" s="71" t="inlineStr">
+        <is>
+          <t>C1: sistemul de personaje + Character Select + Kazuma cu regulile noi. Apoi un personaj pe etapă, testat de tine înainte de următorul.</t>
+        </is>
+      </c>
+      <c r="E51" s="71" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -564,15 +2188,12 @@
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="5" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Stat (cod)</t>
@@ -650,7 +2271,7 @@
         <v>85</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>95</v>
@@ -660,7 +2281,7 @@
           <t>80 – 130</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -670,7 +2291,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Damage-ul atacului de bază (și baza pentru Heavy, Iaijutsu etc.)</t>
+          <t>Damage-ul atacului de bază</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -698,7 +2319,7 @@
           <t>8 – 13</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -736,7 +2357,7 @@
           <t>0,8 – 1,25</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -774,9 +2395,9 @@
           <t>5 – 7,5</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="J5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>dodge_charges</t>
@@ -812,7 +2433,11 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>exista upgrade-uri care pot creste numarul de dash</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -850,7 +2475,7 @@
           <t>0,85 – 1,1</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -888,7 +2513,7 @@
           <t>0 – 0,10</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -926,7 +2551,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -964,9 +2589,9 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
+      <c r="J10" s="3" t="n"/>
+    </row>
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>life_on_kill</t>
@@ -1002,7 +2627,11 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Toate tipurile de Hp videcat la kill se transforma in lifesteal. Primesti viata/dmg dat catre inamici</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1040,7 +2669,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1078,7 +2707,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1116,9 +2745,9 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
+      <c r="J14" s="3" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>dash_recharge</t>
@@ -1154,7 +2783,7 @@
           <t>0,85 – 1,25</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1192,9 +2821,9 @@
           <t>0,9 – 1,15</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
+      <c r="J16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>perfect_window</t>
@@ -1230,9 +2859,9 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
+      <c r="J17" s="3" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>perfect_slow_bonus</t>
@@ -1268,7 +2897,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1306,7 +2935,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1344,7 +2973,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1382,7 +3011,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1420,7 +3049,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1458,7 +3087,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1496,7 +3125,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1534,7 +3163,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1572,7 +3201,7 @@
           <t>0,9 – 1,25</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1610,7 +3239,7 @@
           <t>0,9 – 1,2</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1648,7 +3277,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1686,7 +3315,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1724,7 +3353,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1762,7 +3391,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1800,7 +3429,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1838,7 +3467,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1876,7 +3505,7 @@
           <t>1,0 – 1,3</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1914,9 +3543,9 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36">
+      <c r="J35" s="3" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>ultimate_hit_charge</t>
@@ -1952,7 +3581,7 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr"/>
+      <c r="J36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1990,9 +3619,9 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38">
+      <c r="J37" s="3" t="n"/>
+    </row>
+    <row r="38" ht="30" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>shop_technique_mult</t>
@@ -2028,9 +3657,9 @@
           <t>neschimbat</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39">
+      <c r="J38" s="3" t="n"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
           <t>starting_corruption</t>
@@ -2066,30 +3695,21 @@
           <t>0 – 25</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
           <t>Gri = nu se schimbă între personaje (propunere). Galben = poți modifica. Rândul cursiv e un stat care nu există încă.</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2098,8 +3718,7 @@
   <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
@@ -2109,1081 +3728,1173 @@
     <col width="36" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Personaj</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Tip rând</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Variantă</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Nume / Armă</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Descriere (RO)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Implementare</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Decizie</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Comentarii</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Kazuma</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Rol</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>Ronin duelist</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>Echilibrat, precis, jucat pe timing (Perfect Dodge, Iaijutsu, Kaeshi). HP și damage peste medie, viteză medie. Personajul de bază al jocului.</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="30" t="inlineStr">
         <is>
           <t>Există</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="H2" s="41" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="I2" s="42" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Kazuma</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Armă</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Katana</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Tăieturi precise în arc. Arma actuală din joc.</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t>Există</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="H3" s="43" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="I3" s="44" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Kazuma</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Pasivă</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Keen Eye</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>+8% șansă critică permanent. Se potrivește cu duelistul precis și cu upgrade-urile de critic.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Stat existent</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="43" t="n"/>
+      <c r="I4" s="44" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Kazuma</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Pasivă</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Calm Mind</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Perfect Dodge-ul îți dă și 10% Flow în Kata.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Cod nou (mic)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="30" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="H5" s="43" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="I5" s="44" t="n"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Kazuma</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Pasivă</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Ronin's Focus</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Primul atac după fiecare Perfect Dodge e critic garantat.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Cod nou (mic)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="31" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="H6" s="45" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="I6" s="46" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Rol</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>Dansatoare de lame</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>Rapidă și fragilă: mai puțină viață și damage, dar viteză de mișcare, atac și dash peste medie. Stil de hit-and-run, multe lovituri mici.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="32" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="41" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="I7" s="42" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Armă</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Kodachi duble</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Două lame scurte: lovituri foarte rapide, rază mică. Recomandarea mea.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>Cod nou + model</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="43" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="I8" s="44" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Armă</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Kusarigama</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Seceră cu lanț: rază mare, ritm mai lent.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>Cod nou + model</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="H9" s="43" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="I9" s="44" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Armă</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Tessen (evantaie de luptă)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Evantaie de oțel: arcuri largi și rapide, foarte elegant.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>Cod nou + model</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="H10" s="43" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="I10" s="44" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Pasivă</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Dream Step</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Fereastra Perfect Dodge e cu 25% mai mare (ajută cel care se bazează pe dash).</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>Stat existent</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="H11" s="43" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="I11" s="44" t="n"/>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Pasivă</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Light Feet</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Primul atac după fiecare dash face +20% damage.</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Butterfly Twist</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Dodge-ul (buttefly twist) - atunci cand Yume face dash arunca 3 shuriken in evantai in directia opusa dash-ului (daca dash-ul se face in spate, proiectielel merg in fata) (damage/ shuriken: 5)</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Cod nou (mic)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="H12" s="43" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="I12" s="44" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>Pasivă</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>Moonlit Haste</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>+15% viteză de mișcare cât timp nu ești lovit în ultimele 3 s.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>Cod nou (mic)</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="34" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="H13" s="45" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="I13" s="46" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>Rol</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>General rezistent</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>Lent și greu de oprit: mult HP și damage, primește mai puțin damage, Heavy-ul (RMB, Finisher-ul Kata) lovește mai tare și mai departe.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="35" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="H14" s="41" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="I14" s="42" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Armă</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Naginata</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Lance cu lamă: rază mare, înțepături și mături lente. Recomandarea mea.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Cod nou + model</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="H15" s="43" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="I15" s="44" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Armă</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Odachi (sabie uriașă)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Sabie de două mâini: arcuri enorme, foarte lent.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>Cod nou + model</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="H16" s="43" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="I16" s="44" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>Armă</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Ōtsuchi (ciocan de război)</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Lovituri de zdrobire cu unde de șoc.</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Kanabō</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Lovituri de zdrobire, knock back si cu unde de șoc.</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Cod nou + model</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr"/>
+      <c r="H17" s="43" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="I17" s="44" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>Pasivă</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Unyielding</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Prima lovitură primită în fiecare cameră face 50% mai puțin.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>Cod nou (mic)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="H18" s="43" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="I18" s="44" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>Pasivă</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Heavy Hand</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Heavy-ul (RMB) are +15% damage și +10% rază.</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Heavy-ul (RMB) are +15% damage și +10% rază. RMB da Knockback inamicilor</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Stat existent</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="H19" s="43" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="I19" s="44" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>Pasivă</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>Commander's Presence</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>Inamicii din apropiere (3 m) se mișcă cu 10% mai încet.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="24" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="37" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="H20" s="45" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="I20" s="46" t="n"/>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>Rol</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="26" t="inlineStr">
         <is>
           <t>Blestemul nopții</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="26" t="inlineStr">
         <is>
           <t>Risc / recompensă: începe cu puțin Corruption, bleed mai puternic, se joacă în jurul stării Possessed. Echilibrat ca stat-uri, puternic prin sistemul de Corruption.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="38" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
+      <c r="H21" s="41" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="I21" s="42" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Armă</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>Katana blestemată</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>Lamă neagră cu bleed la lovituri. Recomandarea mea.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>Cod nou + model</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr"/>
+      <c r="H22" s="43" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="I22" s="44" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>Armă</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>Coasă (kama)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>Arc larg și lent, bleed. Rază medie.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>Cod nou + model</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="3" t="inlineStr"/>
+      <c r="H23" s="43" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="I23" s="44" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>Armă</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>Gheare de oțel (tekko-kagi)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>Lovituri rapide la distanță mică, foarte agresiv.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>Cod nou + model</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="3" t="inlineStr"/>
+      <c r="H24" s="43" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="I24" s="44" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>Pasivă</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>Hungry Shadow</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Corruption crește cu 50% mai repede din kill-uri.</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>8% șansă de aplica bleed inamicilor, din orice tip de lovitura.</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>Cod nou (mic)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="H25" s="43" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="I25" s="44" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>Pasivă</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>Long Possession</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>Possessed durează cu 5 secunde mai mult.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t>Cod nou (mic)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="H26" s="43" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="I26" s="44" t="n"/>
+    </row>
+    <row r="27" ht="30.75" customHeight="1" thickBot="1">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t>Pasivă</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
         <is>
           <t>Born Cursed</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="29" t="inlineStr">
         <is>
           <t>Începi fiecare run cu 15% Corruption, iar Cursed sunt deblocate din start.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="29" t="inlineStr">
         <is>
           <t>Stat nou (starting_corruption)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="40" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="3" t="inlineStr"/>
+      <c r="H27" s="45" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="I27" s="46" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Alege O SINGURĂ pasivă per personaj (A/B/C) și O arme per personaj. Dacă vrei să combini sau să inventezi, scrie în Comentarii.</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3195,7 +4906,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3212,2277 +4923,2486 @@
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" style="58" min="9" max="9"/>
+    <col width="34" customWidth="1" style="58" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Personaj</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Var.</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Nume</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Descriere (RO)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Legătură cu Kata / sinergie</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Implementare</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="54" t="inlineStr">
         <is>
           <t>Decizie</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Comentarii</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="49" t="inlineStr">
         <is>
           <t>Kazuma</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="50" t="inlineStr">
         <is>
           <t>LMB</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="50" t="inlineStr">
         <is>
           <t>Katana Slash</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="50" t="inlineStr">
         <is>
           <t>Lovituri rapide în arc, în direcția mouse-ului.</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="50" t="inlineStr">
         <is>
           <t>Lovitura ușoară dă Flow după tehnici.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="59" t="inlineStr">
         <is>
           <t>Există</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="I2" s="63" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="J2" s="55" t="inlineStr">
+        <is>
+          <t>DMG 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>Kazuma</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>RMB</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Lovitură puternică în arc larg după o scurtă pregătire. Este Finisher-ul Kata-ului.</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Finisher: forma o schimbă tehnicile.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="30" t="inlineStr">
         <is>
           <t>Există</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="I3" s="64" t="inlineStr">
+        <is>
+          <t>MODIFIC</t>
+        </is>
+      </c>
+      <c r="J3" s="56" t="inlineStr">
+        <is>
+          <t>DMG 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>Kazuma</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Iaijutsu</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Tăietură-dash în linie dreaptă, invulnerabil în timpul ei.</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Opening / Flow (Crescent Entry, Skill Weaver).</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="30" t="inlineStr">
         <is>
           <t>Există</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="I4" s="64" t="inlineStr">
+        <is>
+          <t>MODIFIC</t>
+        </is>
+      </c>
+      <c r="J4" s="56" t="inlineStr">
+        <is>
+          <t>DMG 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>Kazuma</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Kaeshi</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Postură de contra: prima lovitură primită e anulată și răspunsă cu o tăietură în jur.</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Opening (Shadow Vault) la contra reușită.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="30" t="inlineStr">
         <is>
           <t>Există</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="I5" s="64" t="inlineStr">
+        <is>
+          <t>MODIFIC</t>
+        </is>
+      </c>
+      <c r="J5" s="56" t="inlineStr">
+        <is>
+          <t>DMG: intoarce 40% din atacul parat al unui Inamic. *Daca mai multi inamici sunt in raza de contraatc, toti primesc acel damage, reflectat de un singur inamic (primul care initiaza un atac complet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A6" s="52" t="inlineStr">
         <is>
           <t>Kazuma</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="53" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="53" t="inlineStr">
         <is>
           <t>Moonlit Storm</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="53" t="inlineStr">
         <is>
           <t>Ultimate: furtună de lame, se încarcă din kill-uri.</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="53" t="inlineStr">
         <is>
           <t>Skill Weaver la start.</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="60" t="inlineStr">
         <is>
           <t>Există</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="I6" s="65" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="J6" s="57" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="48" t="inlineStr">
         <is>
           <t>LMB</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="48" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="48" t="inlineStr">
         <is>
           <t>Twin Cuts</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Două tăieturi foarte rapide la fiecare apăsare, rază mică; ritm de hit-and-run.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" s="48" t="inlineStr">
+        <is>
+          <t>Teieturi rapide la fiecare apăsare, rază mică; ritm de hit-and-run.</t>
+        </is>
+      </c>
+      <c r="F7" s="48" t="inlineStr">
         <is>
           <t>Multe lovituri = Flow repede (Crimson Rhythm, Dancing Blade).</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="48" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="61" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="I7" s="63" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="J7" s="55" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>LMB</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Fan of Blades</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Un evantai de 3 tăieturi scurte într-un arc larg.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>Bun la lovituri în spate / Thousand Cuts.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
+      <c r="I8" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J8" s="56" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>LMB</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Dance Step</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Fiecare lovitură o împinge ușor înainte spre țintă, ca un dans.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>Ajută la ținut Kata deschis fără dash.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="I9" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J9" s="56" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>RMB</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Crossing Blades</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Două tăieturi în X în fața ei (Finisher), damage mare în centru.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>Finisher compatibil cu toate tehnicile (Twin Fang, Moon Sever).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
+      <c r="I10" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J10" s="56" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>RMB</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Blade Waltz</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Se rotește 360° cu lamele (rapid, rază medie).</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>Merge cu Whirlwind / Spirit Cleave.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="I11" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J11" s="56" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>RMB</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Leaping Cut</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Sare peste inamic și taie în spate (Finisher).</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Sinergie cu Backstab Rhythm, Ghost Step.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="I12" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="J12" s="56" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Phantom Step</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Teleportare scurtă (4 m) care lasă o clonă ce taie în urmă.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Butterfly Twist scurt (4 m) care lasă o clonă ce taie în urmă.</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>Opening / Flow prin skill; Perfect Dodge-friendly.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr"/>
+      <c r="I13" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="J13" s="56" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Wind Dash</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Dash cu 3 tăieturi pe drum.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Dancing Blade, Crescent-like Openings.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="3" t="inlineStr"/>
+      <c r="I14" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J14" s="56" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Over the Shoulder</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Sare peste cel mai apropiat inamic și aterizează în spatele lui.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Backstab / Ghost Step.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="3" t="inlineStr"/>
+      <c r="I15" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J15" s="56" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Veil of Mist</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Devii invizibilă 1,5 s (inamicii pierd ținta, nu atacă nou).</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Hide existent (Vanish).</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>Cod nou (mic)</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
+      <c r="I16" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J16" s="56" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Smoke Bomb</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>O zonă de fum încetinește inamicii 2 s.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Ajută la ținut Kata deschis.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="I17" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J17" s="56" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Mirror Dream</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>O iluzie îi atrage atacurile 2 s și apoi explodează.</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>O iluzie îi atrage atacurile 2 s și apoi explodează. (explozia afecteaz numai inamicii)</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Contra-skill (ca Kaeshi, alt stil).</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
+      <c r="I18" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="J18" s="56" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Kunai Storm</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Aruncă 12 kunai în cerc, fiecare lovește tare.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Se încarcă din kill-uri; Skill Weaver.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
+      <c r="I19" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J19" s="56" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Dream Clones</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>3 clone atacă 4 secunde.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>Clone ajută la multe lovituri.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="33" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="I20" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="J20" s="56" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Yume</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>Moon Dance</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="19" t="inlineStr">
         <is>
           <t>4 s de viteză +40% și dash fără cooldown.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>Perfect Dodge-uri multe = slow-uri.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="19" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="34" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="I21" s="66" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J21" s="62" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>LMB</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>Long Thrust</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>Înțepătură lungă în linie, lentă, cu rază mare.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>Lovituri rare = Flow din critice, nu din ritm.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="35" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr"/>
+      <c r="I22" s="63" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J22" s="55" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>LMB</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Wide Sweep</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Mătură lentă într-un arc de 200°.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>Bun cu Spirit Cleave.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="13" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr"/>
+      <c r="I23" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="J23" s="56" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>LMB</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Naginata Chain</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>Lanț de 3 lovituri; a treia mătură mai mare.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>Crimson Rhythm.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr"/>
+      <c r="I24" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J24" s="56" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>RMB</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Earth Crush</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>Lovitură verticală cu undă de șoc în fața lui.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>Finisher greu: Tremor, Shatter.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="13" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
+      <c r="I25" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="J25" s="56" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>RMB</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>Steel Sweep</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>Mătură de 360° care împinge inamicii.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>Whirlwind, Crimson Rain.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr"/>
+      <c r="I26" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J26" s="56" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>RMB</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>Piercing Lance</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>Înjunghiere foarte lungă care trece prin mai mulți inamici.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>Gale Slash, Twin Fang.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="13" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I27" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J27" s="56" t="n"/>
+    </row>
+    <row r="28" ht="75" customHeight="1">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Shield Charge</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Înaintează 4 m cu scutul și împinge inamicii (invulnerabil la început).</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Înaintează 4 m cu umarul și împinge inamicii (invulnerabil la început).
+Daca inamicii sunt impinsi intr-un obstacol/perete devin ametiti.
+Dash-ul lui Takeda trebuie sa aiba un cooldown putin mai mare fata de restul caracterelor.</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>Opening / Flow prin skill.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="3" t="inlineStr"/>
+      <c r="I28" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="J28" s="56" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>General's Step</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Lovește podeaua și amețește inamicii din fața lui.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="13" t="inlineStr">
         <is>
           <t>Shatter-like.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="13" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="3" t="inlineStr"/>
+      <c r="I29" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J29" s="56" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Heavy Leap</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>Sare greu și aterizează cu o zonă de damage.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>Storm Step.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="13" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr"/>
-      <c r="J30" s="3" t="inlineStr"/>
+      <c r="I30" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J30" s="56" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Parry Wall</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Parează o lovitură și răspunde cu o împingere puternică.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>Contra-skill (ca Kaeshi).</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="13" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr"/>
-      <c r="J31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I31" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J31" s="56" t="n"/>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>Stone Stance</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>2 s de postură nemișcată: primești cu 60% mai puțin damage.</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>Primesti armura timp de 5 secunde: primești cu 60% mai puțin damage.</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>Protejează Kata cât stai.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="13" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="3" t="inlineStr"/>
+      <c r="I32" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="J32" s="56" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>War Cry</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Inamicii din jur încetinesc 2 s; tu ai +20% viteză de atac 4 s.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>Flow mai repede.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="13" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
-      <c r="J33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I33" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J33" s="56" t="n"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>The Mountain</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Zonă mare de damage la sol timp de 4 s.</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>Unde de soc in jurul inamicului timp de de 5 s. (undele se muta o data cu jucatorul, acesta ramanand in centrul lor)</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>Se încarcă din kill-uri.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="13" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="3" t="inlineStr"/>
+      <c r="I34" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="J34" s="56" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>Phantom Army</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>Soldați spectrali înaintează și lovesc în față.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="13" t="inlineStr">
         <is>
           <t>Skill Weaver.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="13" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" s="36" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I35" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J35" s="56" t="n"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>Takeda</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="24" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="24" t="inlineStr">
         <is>
           <t>General's Fury</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>5 s cu +50% damage și +30% rază.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" s="24" t="inlineStr">
         <is>
           <t>Heavy mai puternic.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="24" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" s="37" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I36" s="66" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J36" s="62" t="n"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>LMB</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>Cursed Edge</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="26" t="inlineStr">
         <is>
           <t>Lovituri cu o șansă mică de bleed.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="26" t="inlineStr">
         <is>
           <t>Bleed build (Crow Feather, Soul Syphon).</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="26" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H37" s="38" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
+      <c r="I37" s="63" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="J37" s="55" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>LMB</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="14" t="inlineStr">
         <is>
           <t>Shadow Claws</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="14" t="inlineStr">
         <is>
           <t>Lovituri rapide scurte care ating 2 inamici.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" s="14" t="inlineStr">
         <is>
           <t>Flow rapid.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr"/>
-      <c r="J38" s="3" t="inlineStr"/>
+      <c r="I38" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J38" s="56" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>LMB</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>Moon Scythe</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>Arc larg și lent, aplică bleed.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>Bleed build.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H39" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr"/>
+      <c r="I39" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J39" s="56" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>RMB</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" s="14" t="inlineStr">
         <is>
           <t>Blood Cut</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" s="14" t="inlineStr">
         <is>
           <t>Finisher care aplică bleed pe toate țintele (3 stack-uri).</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" s="14" t="inlineStr">
         <is>
           <t>Crimson Rain, Blood Harvest.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H40" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr"/>
-      <c r="J40" s="3" t="inlineStr"/>
+      <c r="I40" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="J40" s="56" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>RMB</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="14" t="inlineStr">
         <is>
           <t>Rend</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="14" t="inlineStr">
         <is>
           <t>Finisher care consumă bleed-ul de pe țintă pentru damage imediat.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>Sinergie cu bleed.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H41" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr"/>
+      <c r="I41" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J41" s="56" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>RMB</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="14" t="inlineStr">
         <is>
           <t>Dark Wave</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" s="14" t="inlineStr">
         <is>
           <t>Undă întunecată care trece prin inamici și dă Corruption.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" s="14" t="inlineStr">
         <is>
           <t>Gale Slash.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="14" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H42" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr"/>
-      <c r="J42" s="3" t="inlineStr"/>
+      <c r="I42" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J42" s="56" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>Shadow Pass</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="14" t="inlineStr">
         <is>
           <t>Dash prin inamici care lasă o zonă de bleed.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" s="14" t="inlineStr">
         <is>
           <t>Opening / Flow prin skill.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="14" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H43" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="3" t="inlineStr"/>
+      <c r="I43" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="J43" s="56" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" s="14" t="inlineStr">
         <is>
           <t>Chain Pull</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="14" t="inlineStr">
         <is>
           <t>Un lanț trage cel mai apropiat inamic spre tine.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" s="14" t="inlineStr">
         <is>
           <t>Pregătește Finisher-ul.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" s="14" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H44" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr"/>
+      <c r="I44" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J44" s="56" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>Shadow Throw</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="14" t="inlineStr">
         <is>
           <t>Aruncă o umbră și te teleportezi la ea.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" s="14" t="inlineStr">
         <is>
           <t>Backstab.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="14" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H45" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr"/>
-      <c r="J45" s="3" t="inlineStr"/>
+      <c r="I45" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J45" s="56" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="14" t="inlineStr">
         <is>
           <t>Absorb</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="14" t="inlineStr">
         <is>
           <t>Consumă 20 Corruption pentru a vindeca 15% HP.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" s="14" t="inlineStr">
         <is>
           <t>Controlează Corruption.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H46" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr"/>
+      <c r="I46" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="J46" s="56" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>Black Veil</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="14" t="inlineStr">
         <is>
           <t>Contra: prima lovitură primită e anulată și dă Corruption.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" s="14" t="inlineStr">
         <is>
           <t>Contra-skill (ca Kaeshi).</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H47" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr"/>
-      <c r="J47" s="3" t="inlineStr"/>
+      <c r="I47" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J47" s="56" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" s="14" t="inlineStr">
         <is>
           <t>Echo</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" s="14" t="inlineStr">
         <is>
           <t>Repetă ultima ta lovitură ca o umbră.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" s="14" t="inlineStr">
         <is>
           <t>Flow.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" s="14" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H48" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr"/>
-      <c r="J48" s="3" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I48" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J48" s="56" t="n"/>
+    </row>
+    <row r="49" ht="45" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>Awakening</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Intri imediat în Possessed (de la 50% Corruption în sus), bara se golește normal.</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>Intri imediat în Possessed (de la 50% Corruption în sus), bara se golește normal. Efectele de Possessed sunt mai mari decat la celelalte caractere.</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
         <is>
           <t>Se leagă direct de Corruption / Possessed.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="14" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H49" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="3" t="inlineStr"/>
+      <c r="I49" s="64" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="J49" s="56" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="27" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr">
         <is>
           <t>Endless Night</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" s="14" t="inlineStr">
         <is>
           <t>Zonă întunecată mare: inamicii primesc bleed cât stau în ea.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" s="14" t="inlineStr">
         <is>
           <t>Bleed build.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" s="14" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H50" s="39" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr"/>
-      <c r="J50" s="3" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I50" s="64" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J50" s="56" t="n"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A51" s="28" t="inlineStr">
         <is>
           <t>Kurotsuki</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="29" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" s="29" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="29" t="inlineStr">
         <is>
           <t>Hunger</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="29" t="inlineStr">
         <is>
           <t>6 s în care kill-urile dau dublu Corruption și te vindecă.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" s="29" t="inlineStr">
         <is>
           <t>Corruption / Possessed.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="29" t="inlineStr">
         <is>
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H51" s="40" t="inlineStr">
         <is>
           <t>Propus</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr"/>
-      <c r="J51" s="3" t="inlineStr"/>
+      <c r="I51" s="65" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="J51" s="57" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Alege câte O variantă (A/B/C) per slot și personaj. RMB rămâne mereu Finisher-ul Kata-ului. Poți schimba nume, efecte sau inventa altele în Comentarii.</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -5494,7 +7414,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5564,8 +7484,12 @@
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -5588,10 +7512,14 @@
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Silk Step</t>
@@ -5612,8 +7540,12 @@
           <t>Cod nou (există Vanish)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -5636,8 +7568,12 @@
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -5660,8 +7596,12 @@
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -5684,8 +7624,12 @@
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -5708,8 +7652,12 @@
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -5732,8 +7680,12 @@
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -5756,8 +7708,12 @@
           <t>Cod nou</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -5780,8 +7736,12 @@
           <t>Cod nou (mic)</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -5804,8 +7764,12 @@
           <t>Cod nou (mic)</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -5828,8 +7792,12 @@
           <t>Stat existent</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -5841,13 +7809,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5856,10 +7824,11 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="89" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="26.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Personaj</t>
@@ -5893,6 +7862,11 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Identitate într-o frază</t>
+        </is>
+      </c>
+      <c r="H1" s="67" t="inlineStr">
+        <is>
+          <t>RMB</t>
         </is>
       </c>
     </row>
@@ -5922,6 +7896,11 @@
           <t>Duelistul precis: critice, Perfect Dodge, contra.</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plus 4 dmg fata de light atac </t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -5949,6 +7928,11 @@
           <t>Hit-and-run rapid: viață puțină, multe lovituri mici.</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plus 4 dmg fata de light atac </t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -5957,7 +7941,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>12</v>
@@ -5976,6 +7960,11 @@
           <t>Tancul cu Heavy puternic: lent, rezistent, lovituri grele.</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plus 4 dmg fata de light atac </t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -6003,17 +7992,21 @@
           <t>Blestemul: bleed și Corruption, risc mare pentru putere mare.</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plus 4 dmg fata de light atac </t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Valorile se iau din foaia Stats (propunerile de pornire). Dacă le modifici acolo, actualizează și aici.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plus 4 dmg fata de light atac </t>
         </is>
       </c>
     </row>
@@ -6022,13 +8015,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -6041,7 +8034,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CharacterData (Resource): nume, descriere, culoare, stats (suprascrieri ale base_stats), pasivă (UpgradeEffect sau RuleBehavior), armă + câte o scenă de skill pentru LMB / RMB / Shift / Q / E.</t>
@@ -6076,12 +8069,22 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Primul pas după ce confirmi lista: CharacterData + Character Select + Kazuma ca primul personaj (nu se schimbă nimic la joc). Apoi celelalte personaje, pe rând, fiecare testat înainte de următorul.</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Damage-ul atacului Heavy, Q si E trebuie sa fie usor diferit si gandit fata de light atac</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
